--- a/スタッフマスター.xlsx
+++ b/スタッフマスター.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ローカルユーザー_PC-0000278\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9452A6D9-29AD-4F30-BDA4-DAD999342D98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DF22A00-F383-418A-B712-737DEA0167F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{6B59E9A4-843C-4428-B566-3D6F670A8F75}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="129">
   <si>
     <t>社員番号</t>
   </si>
@@ -348,13 +348,6 @@
   </si>
   <si>
     <t>トップ</t>
-  </si>
-  <si>
-    <t>新宿SC</t>
-    <rPh sb="0" eb="2">
-      <t>シンジュク</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>在宅G</t>
@@ -450,6 +443,13 @@
   </si>
   <si>
     <t>久保園大士0601</t>
+  </si>
+  <si>
+    <t>現場G</t>
+    <rPh sb="0" eb="2">
+      <t>ゲンバ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -844,7 +844,7 @@
   <cols>
     <col min="1" max="1" width="10.75" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -870,10 +870,10 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="D2" t="s">
-        <v>32</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -884,7 +884,7 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D3" t="s">
         <v>101</v>
@@ -898,7 +898,7 @@
         <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D4" t="s">
         <v>33</v>
@@ -912,7 +912,7 @@
         <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D5" t="s">
         <v>33</v>
@@ -926,7 +926,7 @@
         <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D6" t="s">
         <v>101</v>
@@ -940,7 +940,7 @@
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D7" t="s">
         <v>33</v>
@@ -954,7 +954,7 @@
         <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D8" t="s">
         <v>33</v>
@@ -968,7 +968,7 @@
         <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D9" t="s">
         <v>33</v>
@@ -982,7 +982,7 @@
         <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D10" t="s">
         <v>33</v>
@@ -996,7 +996,7 @@
         <v>22</v>
       </c>
       <c r="C11" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D11" t="s">
         <v>33</v>
@@ -1010,7 +1010,7 @@
         <v>24</v>
       </c>
       <c r="C12" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D12" t="s">
         <v>33</v>
@@ -1024,7 +1024,7 @@
         <v>26</v>
       </c>
       <c r="C13" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -1035,7 +1035,7 @@
         <v>28</v>
       </c>
       <c r="C14" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -1046,7 +1046,7 @@
         <v>30</v>
       </c>
       <c r="C15" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -1057,7 +1057,7 @@
         <v>37</v>
       </c>
       <c r="C16" t="s">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="D16" t="s">
         <v>32</v>
@@ -1071,7 +1071,7 @@
         <v>39</v>
       </c>
       <c r="C17" t="s">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="D17" t="s">
         <v>32</v>
@@ -1085,7 +1085,7 @@
         <v>41</v>
       </c>
       <c r="C18" t="s">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="D18" t="s">
         <v>100</v>
@@ -1099,7 +1099,7 @@
         <v>43</v>
       </c>
       <c r="C19" t="s">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="D19" t="s">
         <v>101</v>
@@ -1113,7 +1113,7 @@
         <v>45</v>
       </c>
       <c r="C20" t="s">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="D20" t="s">
         <v>101</v>
@@ -1127,7 +1127,7 @@
         <v>47</v>
       </c>
       <c r="C21" t="s">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="D21" t="s">
         <v>101</v>
@@ -1141,7 +1141,7 @@
         <v>49</v>
       </c>
       <c r="C22" t="s">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="D22" t="s">
         <v>101</v>
@@ -1155,7 +1155,7 @@
         <v>51</v>
       </c>
       <c r="C23" t="s">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="D23" t="s">
         <v>101</v>
@@ -1169,7 +1169,7 @@
         <v>53</v>
       </c>
       <c r="C24" t="s">
-        <v>102</v>
+        <v>128</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -1180,7 +1180,7 @@
         <v>55</v>
       </c>
       <c r="C25" t="s">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="D25" t="s">
         <v>101</v>
@@ -1194,7 +1194,7 @@
         <v>57</v>
       </c>
       <c r="C26" t="s">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="D26" t="s">
         <v>101</v>
@@ -1208,7 +1208,7 @@
         <v>59</v>
       </c>
       <c r="C27" t="s">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="D27" t="s">
         <v>101</v>
@@ -1222,7 +1222,7 @@
         <v>61</v>
       </c>
       <c r="C28" t="s">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="D28" t="s">
         <v>101</v>
@@ -1236,7 +1236,7 @@
         <v>63</v>
       </c>
       <c r="C29" t="s">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="D29" t="s">
         <v>101</v>
@@ -1250,7 +1250,7 @@
         <v>65</v>
       </c>
       <c r="C30" t="s">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="D30" t="s">
         <v>101</v>
@@ -1264,7 +1264,7 @@
         <v>67</v>
       </c>
       <c r="C31" t="s">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="D31" t="s">
         <v>101</v>
@@ -1278,7 +1278,7 @@
         <v>69</v>
       </c>
       <c r="C32" t="s">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="D32" t="s">
         <v>101</v>
@@ -1292,7 +1292,7 @@
         <v>71</v>
       </c>
       <c r="C33" t="s">
-        <v>102</v>
+        <v>128</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -1303,7 +1303,7 @@
         <v>73</v>
       </c>
       <c r="C34" t="s">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="D34" t="s">
         <v>101</v>
@@ -1317,7 +1317,7 @@
         <v>75</v>
       </c>
       <c r="C35" t="s">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="D35" t="s">
         <v>101</v>
@@ -1331,7 +1331,7 @@
         <v>77</v>
       </c>
       <c r="C36" t="s">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="D36" t="s">
         <v>33</v>
@@ -1345,7 +1345,7 @@
         <v>79</v>
       </c>
       <c r="C37" t="s">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="D37" t="s">
         <v>33</v>
@@ -1359,7 +1359,7 @@
         <v>81</v>
       </c>
       <c r="C38" t="s">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="D38" t="s">
         <v>33</v>
@@ -1373,7 +1373,7 @@
         <v>83</v>
       </c>
       <c r="C39" t="s">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="D39" t="s">
         <v>33</v>
@@ -1387,7 +1387,7 @@
         <v>85</v>
       </c>
       <c r="C40" t="s">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="D40" t="s">
         <v>33</v>
@@ -1401,7 +1401,7 @@
         <v>87</v>
       </c>
       <c r="C41" t="s">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="D41" t="s">
         <v>33</v>
@@ -1415,7 +1415,7 @@
         <v>89</v>
       </c>
       <c r="C42" t="s">
-        <v>102</v>
+        <v>128</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -1426,7 +1426,7 @@
         <v>91</v>
       </c>
       <c r="C43" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="D43" t="s">
         <v>33</v>
@@ -1440,7 +1440,7 @@
         <v>93</v>
       </c>
       <c r="C44" t="s">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="D44" t="s">
         <v>33</v>
@@ -1454,7 +1454,7 @@
         <v>95</v>
       </c>
       <c r="C45" t="s">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="D45" t="s">
         <v>33</v>
@@ -1462,13 +1462,13 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B46" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C46" t="s">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="D46" t="s">
         <v>33</v>
@@ -1482,7 +1482,7 @@
         <v>97</v>
       </c>
       <c r="C47" t="s">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="D47" t="s">
         <v>34</v>
@@ -1496,7 +1496,7 @@
         <v>99</v>
       </c>
       <c r="C48" t="s">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="D48" t="s">
         <v>35</v>
@@ -1504,13 +1504,13 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" t="s">
+        <v>103</v>
+      </c>
+      <c r="B49" t="s">
         <v>104</v>
       </c>
-      <c r="B49" t="s">
-        <v>105</v>
-      </c>
       <c r="C49" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D49" t="s">
         <v>100</v>
@@ -1518,13 +1518,13 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" t="s">
+        <v>105</v>
+      </c>
+      <c r="B50" t="s">
         <v>106</v>
       </c>
-      <c r="B50" t="s">
-        <v>107</v>
-      </c>
       <c r="C50" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D50" t="s">
         <v>33</v>
@@ -1532,13 +1532,13 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" t="s">
+        <v>107</v>
+      </c>
+      <c r="B51" t="s">
         <v>108</v>
       </c>
-      <c r="B51" t="s">
-        <v>109</v>
-      </c>
       <c r="C51" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D51" t="s">
         <v>33</v>
@@ -1546,13 +1546,13 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" t="s">
+        <v>109</v>
+      </c>
+      <c r="B52" t="s">
         <v>110</v>
       </c>
-      <c r="B52" t="s">
-        <v>111</v>
-      </c>
       <c r="C52" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D52" t="s">
         <v>33</v>
@@ -1560,24 +1560,24 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" t="s">
+        <v>111</v>
+      </c>
+      <c r="B53" t="s">
         <v>112</v>
       </c>
-      <c r="B53" t="s">
-        <v>113</v>
-      </c>
       <c r="C53" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" t="s">
+        <v>113</v>
+      </c>
+      <c r="B54" t="s">
         <v>114</v>
       </c>
-      <c r="B54" t="s">
-        <v>115</v>
-      </c>
       <c r="C54" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D54" t="s">
         <v>33</v>
@@ -1585,13 +1585,13 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" t="s">
+        <v>115</v>
+      </c>
+      <c r="B55" t="s">
         <v>116</v>
       </c>
-      <c r="B55" t="s">
-        <v>117</v>
-      </c>
       <c r="C55" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D55" t="s">
         <v>33</v>
@@ -1599,13 +1599,13 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" t="s">
+        <v>117</v>
+      </c>
+      <c r="B56" t="s">
         <v>118</v>
       </c>
-      <c r="B56" t="s">
+      <c r="C56" t="s">
         <v>119</v>
-      </c>
-      <c r="C56" t="s">
-        <v>102</v>
       </c>
       <c r="D56" t="s">
         <v>35</v>
@@ -1613,13 +1613,13 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" t="s">
+        <v>126</v>
+      </c>
+      <c r="B57" t="s">
         <v>127</v>
       </c>
-      <c r="B57" t="s">
-        <v>128</v>
-      </c>
       <c r="C57" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D57" t="s">
         <v>35</v>
@@ -1647,13 +1647,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -1664,10 +1664,7 @@
         <v>4</v>
       </c>
       <c r="C2">
-        <v>450000</v>
-      </c>
-      <c r="D2" t="s">
-        <v>124</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -1681,7 +1678,7 @@
         <v>600000</v>
       </c>
       <c r="D3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -1695,21 +1692,21 @@
         <v>600000</v>
       </c>
       <c r="D4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
+        <v>103</v>
+      </c>
+      <c r="B5" t="s">
         <v>104</v>
-      </c>
-      <c r="B5" t="s">
-        <v>105</v>
       </c>
       <c r="C5">
         <v>300000</v>
       </c>
       <c r="D5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -1723,7 +1720,7 @@
         <v>380000</v>
       </c>
       <c r="D6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -1937,10 +1934,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
+        <v>105</v>
+      </c>
+      <c r="B26" t="s">
         <v>106</v>
-      </c>
-      <c r="B26" t="s">
-        <v>107</v>
       </c>
       <c r="C26">
         <v>2200</v>
@@ -2025,10 +2022,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
+        <v>117</v>
+      </c>
+      <c r="B34" t="s">
         <v>118</v>
-      </c>
-      <c r="B34" t="s">
-        <v>119</v>
       </c>
       <c r="C34">
         <v>1800</v>
@@ -2080,10 +2077,10 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
+        <v>113</v>
+      </c>
+      <c r="B39" t="s">
         <v>114</v>
-      </c>
-      <c r="B39" t="s">
-        <v>115</v>
       </c>
       <c r="C39">
         <v>1400</v>
@@ -2157,10 +2154,10 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" t="s">
+        <v>109</v>
+      </c>
+      <c r="B46" t="s">
         <v>110</v>
-      </c>
-      <c r="B46" t="s">
-        <v>111</v>
       </c>
       <c r="C46">
         <v>1500</v>
@@ -2168,10 +2165,10 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" t="s">
+        <v>115</v>
+      </c>
+      <c r="B47" t="s">
         <v>116</v>
-      </c>
-      <c r="B47" t="s">
-        <v>117</v>
       </c>
       <c r="C47">
         <v>1500</v>
@@ -2179,10 +2176,10 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" t="s">
+        <v>107</v>
+      </c>
+      <c r="B48" t="s">
         <v>108</v>
-      </c>
-      <c r="B48" t="s">
-        <v>109</v>
       </c>
       <c r="C48">
         <v>2100</v>
@@ -2190,10 +2187,10 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B49" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C49">
         <v>2000</v>
@@ -2201,10 +2198,10 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" t="s">
+        <v>126</v>
+      </c>
+      <c r="B50" t="s">
         <v>127</v>
-      </c>
-      <c r="B50" t="s">
-        <v>128</v>
       </c>
       <c r="C50">
         <v>1600</v>
